--- a/Team-Data/2012-13/1-28-2012-13.xlsx
+++ b/Team-Data/2012-13/1-28-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -754,7 +821,7 @@
         <v>7</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
@@ -799,7 +866,7 @@
         <v>10</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
@@ -942,7 +1009,7 @@
         <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL3" t="n">
         <v>28</v>
@@ -960,7 +1027,7 @@
         <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
@@ -987,13 +1054,13 @@
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA3" t="n">
         <v>14</v>
       </c>
       <c r="BB3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6</v>
+        <v>0.591</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,70 +1110,70 @@
         <v>35.1</v>
       </c>
       <c r="J4" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L4" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="O4" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P4" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R4" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S4" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T4" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W4" t="n">
         <v>7.2</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
         <v>4.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF4" t="n">
         <v>9</v>
@@ -1115,7 +1182,7 @@
         <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1124,7 +1191,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1133,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
@@ -1145,19 +1212,19 @@
         <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU4" t="n">
         <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1172,13 +1239,13 @@
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
         <v>17</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1274,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" t="n">
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>0.25</v>
+        <v>0.256</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="J5" t="n">
         <v>81.8</v>
@@ -1234,19 +1301,19 @@
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O5" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P5" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R5" t="n">
         <v>11.6</v>
@@ -1258,7 +1325,7 @@
         <v>41.1</v>
       </c>
       <c r="U5" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="V5" t="n">
         <v>14.2</v>
@@ -1270,28 +1337,28 @@
         <v>6.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="Z5" t="n">
         <v>19.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC5" t="n">
         <v>-8</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
         <v>30</v>
@@ -1306,7 +1373,7 @@
         <v>18</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
         <v>26</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1330,7 +1397,7 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT5" t="n">
         <v>22</v>
@@ -1342,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
@@ -1354,10 +1421,10 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.614</v>
+        <v>0.605</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
@@ -1413,43 +1480,43 @@
         <v>0.438</v>
       </c>
       <c r="L6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M6" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O6" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="R6" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S6" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T6" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U6" t="n">
         <v>22.7</v>
       </c>
       <c r="V6" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W6" t="n">
         <v>7.1</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
         <v>5.6</v>
@@ -1464,13 +1531,13 @@
         <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
         <v>7</v>
@@ -1497,19 +1564,19 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
         <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
         <v>11</v>
@@ -1518,31 +1585,31 @@
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW6" t="n">
         <v>25</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
         <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>-5</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG7" t="n">
         <v>28</v>
@@ -1679,7 +1746,7 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1858,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN8" t="n">
         <v>11</v>
@@ -1876,7 +1943,7 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
@@ -1903,7 +1970,7 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>22</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -1935,25 +2002,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.609</v>
+        <v>0.6</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="J9" t="n">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="K9" t="n">
         <v>0.467</v>
@@ -1962,28 +2029,28 @@
         <v>6.4</v>
       </c>
       <c r="M9" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N9" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="O9" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P9" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="S9" t="n">
         <v>31.9</v>
       </c>
       <c r="T9" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="U9" t="n">
         <v>23.7</v>
@@ -1992,10 +2059,10 @@
         <v>15.4</v>
       </c>
       <c r="W9" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X9" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y9" t="n">
         <v>6.8</v>
@@ -2004,19 +2071,19 @@
         <v>20.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="AC9" t="n">
         <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF9" t="n">
         <v>9</v>
@@ -2028,7 +2095,7 @@
         <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -2037,13 +2104,13 @@
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM9" t="n">
         <v>18</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>9</v>
@@ -2070,7 +2137,7 @@
         <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
@@ -2079,10 +2146,10 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2207,7 +2274,7 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>22</v>
@@ -2219,7 +2286,7 @@
         <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>26</v>
@@ -2237,7 +2304,7 @@
         <v>27</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
         <v>14</v>
@@ -2258,16 +2325,16 @@
         <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>8</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -2299,40 +2366,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" t="n">
         <v>17</v>
       </c>
       <c r="G11" t="n">
-        <v>0.614</v>
+        <v>0.605</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J11" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M11" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="N11" t="n">
         <v>0.388</v>
       </c>
       <c r="O11" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P11" t="n">
         <v>21.4</v>
@@ -2347,7 +2414,7 @@
         <v>33.8</v>
       </c>
       <c r="T11" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
         <v>22.7</v>
@@ -2359,28 +2426,28 @@
         <v>7</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y11" t="n">
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.7</v>
+        <v>100.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
@@ -2392,13 +2459,13 @@
         <v>13</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AK11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2428,10 +2495,10 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
@@ -2443,13 +2510,13 @@
         <v>18</v>
       </c>
       <c r="AZ11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -2481,46 +2548,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.532</v>
+        <v>0.522</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J12" t="n">
-        <v>82.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L12" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.361</v>
+        <v>0.358</v>
       </c>
       <c r="O12" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P12" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R12" t="n">
         <v>10.8</v>
@@ -2532,13 +2599,13 @@
         <v>43</v>
       </c>
       <c r="U12" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="W12" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X12" t="n">
         <v>4.1</v>
@@ -2553,16 +2620,16 @@
         <v>19.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.9</v>
+        <v>104.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF12" t="n">
         <v>15</v>
@@ -2574,10 +2641,10 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK12" t="n">
         <v>10</v>
@@ -2589,16 +2656,16 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
         <v>20</v>
@@ -2607,16 +2674,16 @@
         <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
         <v>27</v>
@@ -2625,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>17</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -2663,52 +2730,52 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" t="n">
         <v>26</v>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>0.578</v>
+        <v>0.591</v>
       </c>
       <c r="H13" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="J13" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L13" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.343</v>
+        <v>0.34</v>
       </c>
       <c r="O13" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.739</v>
+        <v>0.74</v>
       </c>
       <c r="R13" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S13" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T13" t="n">
         <v>45.6</v>
@@ -2717,7 +2784,7 @@
         <v>19.8</v>
       </c>
       <c r="V13" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W13" t="n">
         <v>6.8</v>
@@ -2729,31 +2796,31 @@
         <v>5.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>91.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2762,13 +2829,13 @@
         <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN13" t="n">
         <v>24</v>
@@ -2786,7 +2853,7 @@
         <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>2</v>
@@ -2804,19 +2871,19 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2953,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>14</v>
@@ -2968,7 +3035,7 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT14" t="n">
         <v>17</v>
@@ -2977,7 +3044,7 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
@@ -3120,7 +3187,7 @@
         <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>20</v>
@@ -3135,10 +3202,10 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -3162,7 +3229,7 @@
         <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -3180,7 +3247,7 @@
         <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -3209,37 +3276,37 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F16" t="n">
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.659</v>
+        <v>0.651</v>
       </c>
       <c r="H16" t="n">
         <v>48.5</v>
       </c>
       <c r="I16" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J16" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M16" t="n">
         <v>13.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.344</v>
+        <v>0.338</v>
       </c>
       <c r="O16" t="n">
         <v>16.3</v>
@@ -3251,43 +3318,43 @@
         <v>0.79</v>
       </c>
       <c r="R16" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="S16" t="n">
         <v>29.4</v>
       </c>
       <c r="T16" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U16" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="V16" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W16" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y16" t="n">
         <v>6</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3305,7 +3372,7 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AK16" t="n">
         <v>24</v>
@@ -3317,10 +3384,10 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP16" t="n">
         <v>24</v>
@@ -3335,7 +3402,7 @@
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
         <v>23</v>
@@ -3347,19 +3414,19 @@
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BC16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3539,7 @@
         <v>29</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
@@ -3505,10 +3572,10 @@
         <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>13</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-0.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
@@ -3675,13 +3742,13 @@
         <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
         <v>21</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3708,7 +3775,7 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>1</v>
@@ -3720,13 +3787,13 @@
         <v>8</v>
       </c>
       <c r="BA18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB18" t="n">
         <v>13</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3909,7 @@
         <v>18</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
         <v>27</v>
@@ -3869,10 +3936,10 @@
         <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3887,7 +3954,7 @@
         <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>17</v>
@@ -3908,7 +3975,7 @@
         <v>24</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -4015,19 +4082,19 @@
         <v>-3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
       </c>
       <c r="AF20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
         <v>25</v>
       </c>
       <c r="AH20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
         <v>23</v>
@@ -4054,13 +4121,13 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
         <v>19</v>
@@ -4087,10 +4154,10 @@
         <v>26</v>
       </c>
       <c r="BB20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>4.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF21" t="n">
         <v>5</v>
@@ -4212,13 +4279,13 @@
         <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4263,7 +4330,7 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
         <v>18</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>8.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4403,7 +4470,7 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM22" t="n">
         <v>13</v>
@@ -4448,7 +4515,7 @@
         <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -4483,43 +4550,43 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" t="n">
         <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23" t="n">
-        <v>0.318</v>
+        <v>0.326</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="J23" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="O23" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="Q23" t="n">
         <v>0.785</v>
@@ -4528,10 +4595,10 @@
         <v>10.3</v>
       </c>
       <c r="S23" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T23" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
         <v>23.3</v>
@@ -4540,34 +4607,34 @@
         <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="X23" t="n">
         <v>4.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>95</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-4</v>
+        <v>-3.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
         <v>27</v>
       </c>
       <c r="AF23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG23" t="n">
         <v>27</v>
@@ -4576,22 +4643,22 @@
         <v>20</v>
       </c>
       <c r="AI23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK23" t="n">
         <v>8</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>16</v>
       </c>
       <c r="AM23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AN23" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4627,16 +4694,16 @@
         <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E24" t="n">
         <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>0.409</v>
+        <v>0.419</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J24" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.446</v>
+        <v>0.443</v>
       </c>
       <c r="L24" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M24" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O24" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="P24" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="R24" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S24" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T24" t="n">
-        <v>40.8</v>
+        <v>41.1</v>
       </c>
       <c r="U24" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V24" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W24" t="n">
         <v>7.3</v>
@@ -4731,49 +4798,49 @@
         <v>4.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC24" t="n">
         <v>-3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH24" t="n">
         <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,22 +4852,22 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
         <v>23</v>
       </c>
       <c r="AU24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
         <v>17</v>
@@ -4809,16 +4876,16 @@
         <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>-4.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>25</v>
       </c>
       <c r="AF25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG25" t="n">
         <v>26</v>
@@ -4946,13 +5013,13 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL25" t="n">
         <v>25</v>
       </c>
       <c r="AM25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN25" t="n">
         <v>29</v>
@@ -4976,10 +5043,10 @@
         <v>26</v>
       </c>
       <c r="AU25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
         <v>16</v>
@@ -4988,7 +5055,7 @@
         <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5137,13 +5204,13 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO26" t="n">
         <v>17</v>
       </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ26" t="n">
         <v>9</v>
@@ -5152,7 +5219,7 @@
         <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>18</v>
@@ -5164,7 +5231,7 @@
         <v>20</v>
       </c>
       <c r="AW26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
         <v>22</v>
@@ -5173,10 +5240,10 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB26" t="n">
         <v>15</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
         <v>29</v>
       </c>
       <c r="G27" t="n">
-        <v>0.37</v>
+        <v>0.356</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
@@ -5235,13 +5302,13 @@
         <v>0.44</v>
       </c>
       <c r="L27" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M27" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O27" t="n">
         <v>17</v>
@@ -5250,31 +5317,31 @@
         <v>22.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.756</v>
+        <v>0.76</v>
       </c>
       <c r="R27" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S27" t="n">
         <v>28.6</v>
       </c>
       <c r="T27" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z27" t="n">
         <v>21.3</v>
@@ -5286,25 +5353,25 @@
         <v>96.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.3</v>
+        <v>-6.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ27" t="n">
         <v>7</v>
@@ -5313,22 +5380,22 @@
         <v>21</v>
       </c>
       <c r="AL27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM27" t="n">
         <v>20</v>
       </c>
       <c r="AN27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP27" t="n">
         <v>13</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -5343,7 +5410,7 @@
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW27" t="n">
         <v>14</v>
@@ -5358,7 +5425,7 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5553,7 @@
         <v>12</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
@@ -5504,7 +5571,7 @@
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="n">
         <v>23</v>
@@ -5525,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW28" t="n">
         <v>5</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
         <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G29" t="n">
-        <v>0.356</v>
+        <v>0.364</v>
       </c>
       <c r="H29" t="n">
         <v>49</v>
       </c>
       <c r="I29" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J29" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K29" t="n">
         <v>0.445</v>
@@ -5605,7 +5672,7 @@
         <v>21.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O29" t="n">
         <v>17</v>
@@ -5614,19 +5681,19 @@
         <v>22</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R29" t="n">
         <v>10.7</v>
       </c>
       <c r="S29" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T29" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U29" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V29" t="n">
         <v>12.8</v>
@@ -5641,40 +5708,40 @@
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA29" t="n">
         <v>19.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.1</v>
+        <v>-1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
         <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ29" t="n">
         <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL29" t="n">
         <v>10</v>
@@ -5683,10 +5750,10 @@
         <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5695,7 +5762,7 @@
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS29" t="n">
         <v>28</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
@@ -5716,19 +5783,19 @@
         <v>24</v>
       </c>
       <c r="AY29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB29" t="n">
         <v>12</v>
       </c>
       <c r="BC29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -5757,64 +5824,64 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" t="n">
         <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>0.533</v>
+        <v>0.545</v>
       </c>
       <c r="H30" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J30" t="n">
         <v>82</v>
       </c>
       <c r="K30" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L30" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M30" t="n">
         <v>17.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O30" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P30" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.767</v>
+        <v>0.77</v>
       </c>
       <c r="R30" t="n">
         <v>12.4</v>
       </c>
       <c r="S30" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T30" t="n">
         <v>42</v>
       </c>
       <c r="U30" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V30" t="n">
         <v>14.8</v>
       </c>
       <c r="W30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="X30" t="n">
         <v>6.3</v>
@@ -5829,16 +5896,16 @@
         <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.09999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF30" t="n">
         <v>14</v>
@@ -5847,10 +5914,10 @@
         <v>14</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ30" t="n">
         <v>16</v>
@@ -5871,28 +5938,28 @@
         <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU30" t="n">
         <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AX30" t="n">
         <v>6</v>
@@ -5904,13 +5971,13 @@
         <v>26</v>
       </c>
       <c r="BA30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" t="n">
         <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>0.256</v>
+        <v>0.262</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
@@ -5957,34 +6024,34 @@
         <v>35</v>
       </c>
       <c r="J31" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.422</v>
+        <v>0.421</v>
       </c>
       <c r="L31" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M31" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O31" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="P31" t="n">
         <v>20.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.736</v>
+        <v>0.734</v>
       </c>
       <c r="R31" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S31" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T31" t="n">
         <v>43.7</v>
@@ -5993,16 +6060,16 @@
         <v>21.5</v>
       </c>
       <c r="V31" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W31" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z31" t="n">
         <v>20.7</v>
@@ -6014,7 +6081,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-4.8</v>
+        <v>-4.9</v>
       </c>
       <c r="AD31" t="n">
         <v>26</v>
@@ -6035,19 +6102,19 @@
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
       </c>
       <c r="AL31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
@@ -6056,13 +6123,13 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR31" t="n">
         <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT31" t="n">
         <v>8</v>
@@ -6071,13 +6138,13 @@
         <v>20</v>
       </c>
       <c r="AV31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX31" t="n">
         <v>19</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>21</v>
       </c>
       <c r="AY31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-28-2012-13</t>
+          <t>2013-01-28</t>
         </is>
       </c>
     </row>
